--- a/contest_entry_forms/032_health_product_raffle_entry--contest_entry_forms.xlsx
+++ b/contest_entry_forms/032_health_product_raffle_entry--contest_entry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1353,971 +1353,971 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pineapple</t>
+          <t>blueberry</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pineapple</t>
+          <t>Blueberry</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pears</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pears</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>watermelon</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Watermelon</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>blueberry</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blueberry</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>banana</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mango</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>online_ads</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Online Ads</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>grapes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grapes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>avocado</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avocado</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pineapple</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pineapple</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pears</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pears</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>watermelon</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Watermelon</t>
+          <t>Radio</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cherries</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cherries</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>blueberry</t>
+          <t>podcasts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blueberry</t>
+          <t>Podcasts</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>pomegranate</t>
+          <t>online_influencers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pomegranate</t>
+          <t>Online Influencers</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>berries</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Berries</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kiwi</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kiwi</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>apricots</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Apricots</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pears</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pears</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pineapple</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pineapple</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pomegranate</t>
+          <t>online_ads</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pomegranate</t>
+          <t>Online Ads</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>grapes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Grapes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>apricots</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Apricots</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pears</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pears</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pineapple</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pineapple</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pomegranate</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pomegranate</t>
+          <t>Radio</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>product_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>grapes</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Grapes</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>podcasts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Podcasts</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>online_influencers</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Online Influencers</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_prophets_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>friends</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>app</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>App</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>online_ads</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Online Ads</t>
+          <t>In-app</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>in-store</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>In-store</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>word_of_mouth</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Word of Mouth</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>print_media</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Print Media</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>radio</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>tv</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>podcasts</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Podcasts</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>online_influencers</t>
+          <t>google_search</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Online Influencers</t>
+          <t>Google Search</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>how_did_you_enter_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>email_opt_in_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>email_opt_in_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>friends</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>online_ads</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Online Ads</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>word_of_mouth</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Word of Mouth</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>print_media</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Print Media</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>radio</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>tv</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>UK</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>podcasts</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Podcasts</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>online_influencers</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Online Influencers</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>how_prophets_choices</t>
+          <t>country_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2334,525 +2334,66 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>how_did_you_enter_choices</t>
+          <t>agree_terms_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>how_did_you_enter_choices</t>
+          <t>agree_terms_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>app</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>how_did_you_enter_choices</t>
+          <t>agree_privacy_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>in-app</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>In-app</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>how_did_you_enter_choices</t>
+          <t>agree_privacy_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>in-store</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
-        <is>
-          <t>In-store</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>mail</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Mail</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>social_media</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Social Media</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>google_search</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>how_did_you_enter_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>email_opt_in_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>email_opt_in_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>gender_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>gender_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>gender_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>country_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>united_states</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>country_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>canada</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>country_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>mexico</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>country_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>uk</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>country_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>australia</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>country_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>japan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>country_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>agree_terms_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>agree_terms_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>agree_privacy_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>agree_privacy_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
         <is>
           <t>Disagree</t>
         </is>
